--- a/testdata/import/04-catalog-errors.xlsx
+++ b/testdata/import/04-catalog-errors.xlsx
@@ -426,19 +426,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,35 +460,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>ИТ-программа</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Номер договора</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Подписание лицензии</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Срок действия лицензии (год)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Статус по передачи</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ФИО Менеджера</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ответственные от ВУЗа</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -511,26 +517,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Инженер по тестированию</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>ДГ-2026-240</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>2027</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Новиков Сергей Павлович</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Денисов Константин Анатольевич</t>
         </is>
@@ -547,28 +558,28 @@
           <t>Песочница DevOps</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ДГ-2026-241</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2027</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Новиков Сергей Павлович</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Не указан вуз</t>
         </is>
@@ -590,23 +601,23 @@
           <t>Песочница DevOps</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>2027</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Новиков Сергей Павлович</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Не указан номер договора</t>
         </is>
@@ -630,28 +641,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>ДГ-2026-242</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>31.02.2026</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>2027</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Морозова Татьяна Евгеньевна</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Такой даты нет</t>
         </is>
@@ -675,28 +691,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Анализ защищённости приложений</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>ДГ-2026-243</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>бессрочно</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Морозова Татьяна Евгеньевна</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Срок лицензии не разобрать</t>
         </is>
@@ -720,26 +741,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Аналитик данных</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>ДГ-2026-244</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>2027</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Отгружено</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Лебедев Игорь Николаевич</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Такого статуса передачи нет</t>
         </is>
@@ -763,26 +789,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Сетевой инженер</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>ДГ-2026-245</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>2027</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Сидоров Сидор Сидорович</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Менеджера нет среди сотрудников</t>
         </is>
@@ -806,26 +837,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Инженер сетей связи</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ДГ-2026-246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>2027</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Козлова Анастасия Олеговна</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Кудрявцева Юлия Сергеевна</t>
         </is>
